--- a/Urinoir-Matrix.xlsx
+++ b/Urinoir-Matrix.xlsx
@@ -1222,7 +1222,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>43</col>
+      <col>42</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1247,7 +1247,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>44</col>
+      <col>43</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1272,7 +1272,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>45</col>
+      <col>44</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1297,7 +1297,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>48</col>
+      <col>45</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1322,7 +1322,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>51</col>
+      <col>46</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1347,7 +1347,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>52</col>
+      <col>47</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1372,12 +1372,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>48</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="400050"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1397,12 +1397,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>49</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="400050"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1422,12 +1422,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>50</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="400050"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1447,12 +1447,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>51</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="400050"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1472,12 +1472,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>52</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="400050"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1499,7 +1499,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1524,7 +1524,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1549,7 +1549,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1574,7 +1574,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1599,7 +1599,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1624,7 +1624,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1649,7 +1649,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1674,7 +1674,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1699,7 +1699,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1724,7 +1724,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1749,7 +1749,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1774,7 +1774,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1799,7 +1799,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1824,7 +1824,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1849,7 +1849,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1874,7 +1874,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1899,7 +1899,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1924,7 +1924,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1949,7 +1949,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1974,7 +1974,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -1999,7 +1999,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2024,7 +2024,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2049,7 +2049,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2074,7 +2074,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2099,7 +2099,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2124,7 +2124,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2149,7 +2149,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2174,7 +2174,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2199,7 +2199,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2224,7 +2224,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2249,7 +2249,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2274,7 +2274,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2299,7 +2299,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2324,7 +2324,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2349,7 +2349,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2374,7 +2374,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2399,7 +2399,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2424,7 +2424,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2449,7 +2449,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2474,7 +2474,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2499,7 +2499,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2524,7 +2524,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2549,7 +2549,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2574,7 +2574,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2599,7 +2599,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2624,7 +2624,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="400050"/>
@@ -2635,6 +2635,131 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3013,7 +3138,7 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="4" t="inlineStr">
         <is>
-          <t>Immer dabei</t>
+          <t>Montagematerial</t>
         </is>
       </c>
       <c r="P1" s="5" t="n"/>
@@ -3055,28 +3180,28 @@
       <c r="AJ1" s="12" t="n"/>
       <c r="AK1" s="12" t="n"/>
       <c r="AL1" s="12" t="n"/>
-      <c r="AM1" s="13" t="inlineStr">
+      <c r="AM1" s="12" t="n"/>
+      <c r="AN1" s="13" t="inlineStr">
         <is>
           <t>Befestigung</t>
         </is>
       </c>
-      <c r="AN1" s="14" t="n"/>
       <c r="AO1" s="14" t="n"/>
       <c r="AP1" s="14" t="n"/>
-      <c r="AQ1" s="15" t="inlineStr">
+      <c r="AQ1" s="14" t="n"/>
+      <c r="AR1" s="15" t="inlineStr">
         <is>
           <t>Trennwand</t>
         </is>
       </c>
-      <c r="AR1" s="16" t="n"/>
       <c r="AS1" s="16" t="n"/>
       <c r="AT1" s="16" t="n"/>
-      <c r="AU1" s="17" t="inlineStr">
+      <c r="AU1" s="16" t="n"/>
+      <c r="AV1" s="17" t="inlineStr">
         <is>
           <t>Weiteres</t>
         </is>
       </c>
-      <c r="AV1" s="18" t="n"/>
       <c r="AW1" s="18" t="n"/>
       <c r="AX1" s="18" t="n"/>
       <c r="AY1" s="18" t="n"/>
@@ -3114,15 +3239,15 @@
       <c r="AJ2" s="12" t="n"/>
       <c r="AK2" s="12" t="n"/>
       <c r="AL2" s="12" t="n"/>
-      <c r="AM2" s="14" t="n"/>
+      <c r="AM2" s="12" t="n"/>
       <c r="AN2" s="14" t="n"/>
       <c r="AO2" s="14" t="n"/>
       <c r="AP2" s="14" t="n"/>
-      <c r="AQ2" s="16" t="n"/>
+      <c r="AQ2" s="14" t="n"/>
       <c r="AR2" s="16" t="n"/>
       <c r="AS2" s="16" t="n"/>
       <c r="AT2" s="16" t="n"/>
-      <c r="AU2" s="18" t="n"/>
+      <c r="AU2" s="16" t="n"/>
       <c r="AV2" s="18" t="n"/>
       <c r="AW2" s="18" t="n"/>
       <c r="AX2" s="18" t="n"/>
@@ -3278,102 +3403,102 @@
       </c>
       <c r="AD3" s="27" t="inlineStr">
         <is>
+          <t>2141 298</t>
+        </is>
+      </c>
+      <c r="AE3" s="27" t="inlineStr">
+        <is>
           <t>3431 102</t>
         </is>
       </c>
-      <c r="AE3" s="27" t="inlineStr">
+      <c r="AF3" s="27" t="inlineStr">
         <is>
           <t>3431 110</t>
         </is>
       </c>
-      <c r="AF3" s="27" t="inlineStr">
+      <c r="AG3" s="27" t="inlineStr">
         <is>
           <t>3431 250</t>
         </is>
       </c>
-      <c r="AG3" s="27" t="inlineStr">
+      <c r="AH3" s="27" t="inlineStr">
         <is>
           <t>3441 111</t>
         </is>
       </c>
-      <c r="AH3" s="27" t="inlineStr">
+      <c r="AI3" s="27" t="inlineStr">
         <is>
           <t>3441 112</t>
         </is>
       </c>
-      <c r="AI3" s="27" t="inlineStr">
+      <c r="AJ3" s="27" t="inlineStr">
         <is>
           <t>3441 120</t>
         </is>
       </c>
-      <c r="AJ3" s="27" t="inlineStr">
+      <c r="AK3" s="27" t="inlineStr">
         <is>
           <t>3441 150</t>
         </is>
       </c>
-      <c r="AK3" s="27" t="inlineStr">
+      <c r="AL3" s="27" t="inlineStr">
         <is>
           <t>8111 412</t>
         </is>
       </c>
-      <c r="AL3" s="27" t="inlineStr">
+      <c r="AM3" s="27" t="inlineStr">
         <is>
           <t>8111 428</t>
         </is>
       </c>
-      <c r="AM3" s="28" t="inlineStr">
+      <c r="AN3" s="28" t="inlineStr">
         <is>
           <t>3962 155</t>
         </is>
       </c>
-      <c r="AN3" s="28" t="inlineStr">
+      <c r="AO3" s="28" t="inlineStr">
         <is>
           <t>3962 156</t>
         </is>
       </c>
-      <c r="AO3" s="28" t="inlineStr">
+      <c r="AP3" s="28" t="inlineStr">
         <is>
           <t>8211 112</t>
         </is>
       </c>
-      <c r="AP3" s="28" t="inlineStr">
+      <c r="AQ3" s="28" t="inlineStr">
         <is>
           <t>8211 210</t>
         </is>
       </c>
-      <c r="AQ3" s="29" t="inlineStr">
+      <c r="AR3" s="29" t="inlineStr">
         <is>
           <t>2112 890</t>
         </is>
       </c>
-      <c r="AR3" s="29" t="inlineStr">
+      <c r="AS3" s="29" t="inlineStr">
         <is>
           <t>3482 117</t>
         </is>
       </c>
-      <c r="AS3" s="29" t="inlineStr">
+      <c r="AT3" s="29" t="inlineStr">
         <is>
           <t>3482 118</t>
         </is>
       </c>
-      <c r="AT3" s="29" t="inlineStr">
+      <c r="AU3" s="29" t="inlineStr">
         <is>
           <t>3482 119</t>
         </is>
       </c>
-      <c r="AU3" s="30" t="inlineStr">
+      <c r="AV3" s="30" t="inlineStr">
         <is>
           <t>2112 889</t>
         </is>
       </c>
-      <c r="AV3" s="30" t="inlineStr">
+      <c r="AW3" s="30" t="inlineStr">
         <is>
           <t>2121 198</t>
-        </is>
-      </c>
-      <c r="AW3" s="30" t="inlineStr">
-        <is>
-          <t>2141 298</t>
         </is>
       </c>
       <c r="AX3" s="30" t="inlineStr">
@@ -3510,80 +3635,80 @@
       </c>
       <c r="AD4" s="37" t="inlineStr">
         <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="AE4" s="37" t="inlineStr">
+        <is>
           <t>106.00</t>
         </is>
       </c>
-      <c r="AE4" s="37" t="inlineStr">
+      <c r="AF4" s="37" t="inlineStr">
         <is>
           <t>158.00</t>
         </is>
       </c>
-      <c r="AF4" s="37" t="inlineStr">
+      <c r="AG4" s="37" t="inlineStr">
         <is>
           <t>21.00</t>
         </is>
       </c>
-      <c r="AG4" s="37" t="inlineStr">
+      <c r="AH4" s="37" t="inlineStr">
         <is>
           <t>81.50</t>
         </is>
       </c>
-      <c r="AH4" s="37" t="inlineStr">
+      <c r="AI4" s="37" t="inlineStr">
         <is>
           <t>90.50</t>
         </is>
       </c>
-      <c r="AI4" s="37" t="inlineStr"/>
-      <c r="AJ4" s="37" t="inlineStr">
+      <c r="AJ4" s="37" t="inlineStr"/>
+      <c r="AK4" s="37" t="inlineStr">
         <is>
           <t>76.50</t>
         </is>
       </c>
-      <c r="AK4" s="37" t="inlineStr"/>
-      <c r="AL4" s="37" t="inlineStr">
+      <c r="AL4" s="37" t="inlineStr"/>
+      <c r="AM4" s="37" t="inlineStr">
         <is>
           <t>4.80</t>
         </is>
       </c>
-      <c r="AM4" s="38" t="inlineStr">
+      <c r="AN4" s="38" t="inlineStr">
         <is>
           <t>41.50</t>
         </is>
       </c>
-      <c r="AN4" s="38" t="inlineStr">
+      <c r="AO4" s="38" t="inlineStr">
         <is>
           <t>27.00</t>
         </is>
       </c>
-      <c r="AO4" s="38" t="inlineStr"/>
-      <c r="AP4" s="38" t="inlineStr">
+      <c r="AP4" s="38" t="inlineStr"/>
+      <c r="AQ4" s="38" t="inlineStr">
         <is>
           <t>14.50</t>
         </is>
       </c>
-      <c r="AQ4" s="39" t="inlineStr"/>
-      <c r="AR4" s="39" t="inlineStr">
+      <c r="AR4" s="39" t="inlineStr"/>
+      <c r="AS4" s="39" t="inlineStr">
         <is>
           <t>976.00</t>
         </is>
       </c>
-      <c r="AS4" s="39" t="inlineStr">
+      <c r="AT4" s="39" t="inlineStr">
         <is>
           <t>976.00</t>
         </is>
       </c>
-      <c r="AT4" s="39" t="inlineStr">
+      <c r="AU4" s="39" t="inlineStr">
         <is>
           <t>976.00</t>
         </is>
       </c>
-      <c r="AU4" s="40" t="inlineStr"/>
       <c r="AV4" s="40" t="inlineStr"/>
-      <c r="AW4" s="40" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
+      <c r="AW4" s="40" t="inlineStr"/>
       <c r="AX4" s="40" t="inlineStr"/>
       <c r="AY4" s="40" t="inlineStr"/>
       <c r="AZ4" s="40" t="inlineStr">
@@ -3704,27 +3829,27 @@
       </c>
       <c r="AD5" s="44" t="inlineStr"/>
       <c r="AE5" s="44" t="inlineStr"/>
-      <c r="AF5" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AF5" s="44" t="inlineStr"/>
       <c r="AG5" s="48" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="AH5" s="44" t="inlineStr"/>
+      <c r="AH5" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI5" s="44" t="inlineStr"/>
       <c r="AJ5" s="44" t="inlineStr"/>
       <c r="AK5" s="44" t="inlineStr"/>
       <c r="AL5" s="44" t="inlineStr"/>
-      <c r="AM5" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AN5" s="44" t="inlineStr"/>
+      <c r="AM5" s="44" t="inlineStr"/>
+      <c r="AN5" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AO5" s="44" t="inlineStr"/>
       <c r="AP5" s="44" t="inlineStr"/>
       <c r="AQ5" s="44" t="inlineStr"/>
@@ -3732,12 +3857,12 @@
       <c r="AS5" s="44" t="inlineStr"/>
       <c r="AT5" s="44" t="inlineStr"/>
       <c r="AU5" s="44" t="inlineStr"/>
-      <c r="AV5" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AW5" s="44" t="inlineStr"/>
+      <c r="AV5" s="44" t="inlineStr"/>
+      <c r="AW5" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AX5" s="44" t="inlineStr"/>
       <c r="AY5" s="44" t="inlineStr"/>
       <c r="AZ5" s="44" t="inlineStr"/>
@@ -3830,18 +3955,14 @@
       <c r="AK6" s="44" t="inlineStr"/>
       <c r="AL6" s="44" t="inlineStr"/>
       <c r="AM6" s="44" t="inlineStr"/>
-      <c r="AN6" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO6" s="44" t="inlineStr"/>
+      <c r="AN6" s="44" t="inlineStr"/>
+      <c r="AO6" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP6" s="44" t="inlineStr"/>
-      <c r="AQ6" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ6" s="44" t="inlineStr"/>
       <c r="AR6" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -3857,7 +3978,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU6" s="44" t="inlineStr"/>
+      <c r="AU6" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV6" s="44" t="inlineStr"/>
       <c r="AW6" s="44" t="inlineStr"/>
       <c r="AX6" s="44" t="inlineStr"/>
@@ -3952,18 +4077,14 @@
       <c r="AK7" s="44" t="inlineStr"/>
       <c r="AL7" s="44" t="inlineStr"/>
       <c r="AM7" s="44" t="inlineStr"/>
-      <c r="AN7" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO7" s="44" t="inlineStr"/>
+      <c r="AN7" s="44" t="inlineStr"/>
+      <c r="AO7" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP7" s="44" t="inlineStr"/>
-      <c r="AQ7" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ7" s="44" t="inlineStr"/>
       <c r="AR7" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -3979,7 +4100,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU7" s="44" t="inlineStr"/>
+      <c r="AU7" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV7" s="44" t="inlineStr"/>
       <c r="AW7" s="44" t="inlineStr"/>
       <c r="AX7" s="44" t="inlineStr"/>
@@ -4098,34 +4223,30 @@
       </c>
       <c r="AD8" s="44" t="inlineStr"/>
       <c r="AE8" s="44" t="inlineStr"/>
-      <c r="AF8" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG8" s="44" t="inlineStr"/>
+      <c r="AF8" s="44" t="inlineStr"/>
+      <c r="AG8" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH8" s="44" t="inlineStr"/>
       <c r="AI8" s="44" t="inlineStr"/>
-      <c r="AJ8" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK8" s="44" t="inlineStr"/>
+      <c r="AJ8" s="44" t="inlineStr"/>
+      <c r="AK8" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL8" s="44" t="inlineStr"/>
       <c r="AM8" s="44" t="inlineStr"/>
-      <c r="AN8" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO8" s="44" t="inlineStr"/>
+      <c r="AN8" s="44" t="inlineStr"/>
+      <c r="AO8" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP8" s="44" t="inlineStr"/>
-      <c r="AQ8" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ8" s="44" t="inlineStr"/>
       <c r="AR8" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4141,7 +4262,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU8" s="44" t="inlineStr"/>
+      <c r="AU8" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV8" s="44" t="inlineStr"/>
       <c r="AW8" s="44" t="inlineStr"/>
       <c r="AX8" s="44" t="inlineStr"/>
@@ -4236,18 +4361,14 @@
       <c r="AK9" s="44" t="inlineStr"/>
       <c r="AL9" s="44" t="inlineStr"/>
       <c r="AM9" s="44" t="inlineStr"/>
-      <c r="AN9" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO9" s="44" t="inlineStr"/>
+      <c r="AN9" s="44" t="inlineStr"/>
+      <c r="AO9" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP9" s="44" t="inlineStr"/>
-      <c r="AQ9" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ9" s="44" t="inlineStr"/>
       <c r="AR9" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4263,7 +4384,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU9" s="44" t="inlineStr"/>
+      <c r="AU9" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV9" s="44" t="inlineStr"/>
       <c r="AW9" s="44" t="inlineStr"/>
       <c r="AX9" s="44" t="inlineStr"/>
@@ -4358,18 +4483,14 @@
       <c r="AK10" s="44" t="inlineStr"/>
       <c r="AL10" s="44" t="inlineStr"/>
       <c r="AM10" s="44" t="inlineStr"/>
-      <c r="AN10" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO10" s="44" t="inlineStr"/>
+      <c r="AN10" s="44" t="inlineStr"/>
+      <c r="AO10" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP10" s="44" t="inlineStr"/>
-      <c r="AQ10" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ10" s="44" t="inlineStr"/>
       <c r="AR10" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4385,7 +4506,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU10" s="44" t="inlineStr"/>
+      <c r="AU10" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV10" s="44" t="inlineStr"/>
       <c r="AW10" s="44" t="inlineStr"/>
       <c r="AX10" s="44" t="inlineStr"/>
@@ -4504,34 +4629,30 @@
       </c>
       <c r="AD11" s="44" t="inlineStr"/>
       <c r="AE11" s="44" t="inlineStr"/>
-      <c r="AF11" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG11" s="44" t="inlineStr"/>
+      <c r="AF11" s="44" t="inlineStr"/>
+      <c r="AG11" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH11" s="44" t="inlineStr"/>
       <c r="AI11" s="44" t="inlineStr"/>
-      <c r="AJ11" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK11" s="44" t="inlineStr"/>
+      <c r="AJ11" s="44" t="inlineStr"/>
+      <c r="AK11" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL11" s="44" t="inlineStr"/>
       <c r="AM11" s="44" t="inlineStr"/>
-      <c r="AN11" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO11" s="44" t="inlineStr"/>
+      <c r="AN11" s="44" t="inlineStr"/>
+      <c r="AO11" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP11" s="44" t="inlineStr"/>
-      <c r="AQ11" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ11" s="44" t="inlineStr"/>
       <c r="AR11" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4547,7 +4668,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU11" s="44" t="inlineStr"/>
+      <c r="AU11" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV11" s="44" t="inlineStr"/>
       <c r="AW11" s="44" t="inlineStr"/>
       <c r="AX11" s="44" t="inlineStr"/>
@@ -4664,28 +4789,32 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AD12" s="44" t="inlineStr"/>
+      <c r="AD12" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE12" s="44" t="inlineStr"/>
-      <c r="AF12" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG12" s="44" t="inlineStr"/>
+      <c r="AF12" s="44" t="inlineStr"/>
+      <c r="AG12" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH12" s="44" t="inlineStr"/>
       <c r="AI12" s="44" t="inlineStr"/>
-      <c r="AJ12" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK12" s="44" t="inlineStr"/>
-      <c r="AL12" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AM12" s="44" t="inlineStr"/>
+      <c r="AJ12" s="44" t="inlineStr"/>
+      <c r="AK12" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AL12" s="44" t="inlineStr"/>
+      <c r="AM12" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AN12" s="44" t="inlineStr"/>
       <c r="AO12" s="44" t="inlineStr"/>
       <c r="AP12" s="44" t="inlineStr"/>
@@ -4695,11 +4824,7 @@
       <c r="AT12" s="44" t="inlineStr"/>
       <c r="AU12" s="44" t="inlineStr"/>
       <c r="AV12" s="44" t="inlineStr"/>
-      <c r="AW12" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AW12" s="44" t="inlineStr"/>
       <c r="AX12" s="44" t="inlineStr"/>
       <c r="AY12" s="44" t="inlineStr"/>
       <c r="AZ12" s="44" t="inlineStr"/>
@@ -4799,11 +4924,7 @@
       <c r="AN13" s="44" t="inlineStr"/>
       <c r="AO13" s="44" t="inlineStr"/>
       <c r="AP13" s="44" t="inlineStr"/>
-      <c r="AQ13" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ13" s="44" t="inlineStr"/>
       <c r="AR13" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4819,7 +4940,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU13" s="44" t="inlineStr"/>
+      <c r="AU13" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV13" s="44" t="inlineStr"/>
       <c r="AW13" s="44" t="inlineStr"/>
       <c r="AX13" s="44" t="inlineStr"/>
@@ -4938,30 +5063,26 @@
       </c>
       <c r="AD14" s="44" t="inlineStr"/>
       <c r="AE14" s="44" t="inlineStr"/>
-      <c r="AF14" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG14" s="44" t="inlineStr"/>
+      <c r="AF14" s="44" t="inlineStr"/>
+      <c r="AG14" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH14" s="44" t="inlineStr"/>
       <c r="AI14" s="44" t="inlineStr"/>
       <c r="AJ14" s="44" t="inlineStr"/>
-      <c r="AK14" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AL14" s="44" t="inlineStr"/>
+      <c r="AK14" s="44" t="inlineStr"/>
+      <c r="AL14" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AM14" s="44" t="inlineStr"/>
       <c r="AN14" s="44" t="inlineStr"/>
       <c r="AO14" s="44" t="inlineStr"/>
       <c r="AP14" s="44" t="inlineStr"/>
-      <c r="AQ14" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ14" s="44" t="inlineStr"/>
       <c r="AR14" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -4977,7 +5098,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU14" s="44" t="inlineStr"/>
+      <c r="AU14" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV14" s="44" t="inlineStr"/>
       <c r="AW14" s="44" t="inlineStr"/>
       <c r="AX14" s="44" t="inlineStr"/>
@@ -5075,11 +5200,7 @@
       <c r="AN15" s="44" t="inlineStr"/>
       <c r="AO15" s="44" t="inlineStr"/>
       <c r="AP15" s="44" t="inlineStr"/>
-      <c r="AQ15" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ15" s="44" t="inlineStr"/>
       <c r="AR15" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5095,7 +5216,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU15" s="44" t="inlineStr"/>
+      <c r="AU15" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV15" s="44" t="inlineStr"/>
       <c r="AW15" s="44" t="inlineStr"/>
       <c r="AX15" s="44" t="inlineStr"/>
@@ -5214,30 +5339,26 @@
       </c>
       <c r="AD16" s="44" t="inlineStr"/>
       <c r="AE16" s="44" t="inlineStr"/>
-      <c r="AF16" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG16" s="44" t="inlineStr"/>
+      <c r="AF16" s="44" t="inlineStr"/>
+      <c r="AG16" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH16" s="44" t="inlineStr"/>
       <c r="AI16" s="44" t="inlineStr"/>
       <c r="AJ16" s="44" t="inlineStr"/>
-      <c r="AK16" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AL16" s="44" t="inlineStr"/>
+      <c r="AK16" s="44" t="inlineStr"/>
+      <c r="AL16" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AM16" s="44" t="inlineStr"/>
       <c r="AN16" s="44" t="inlineStr"/>
       <c r="AO16" s="44" t="inlineStr"/>
       <c r="AP16" s="44" t="inlineStr"/>
-      <c r="AQ16" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ16" s="44" t="inlineStr"/>
       <c r="AR16" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5253,7 +5374,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU16" s="44" t="inlineStr"/>
+      <c r="AU16" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV16" s="44" t="inlineStr"/>
       <c r="AW16" s="44" t="inlineStr"/>
       <c r="AX16" s="44" t="inlineStr"/>
@@ -5331,19 +5456,15 @@
       <c r="AJ17" s="44" t="inlineStr"/>
       <c r="AK17" s="44" t="inlineStr"/>
       <c r="AL17" s="44" t="inlineStr"/>
-      <c r="AM17" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AN17" s="44" t="inlineStr"/>
+      <c r="AM17" s="44" t="inlineStr"/>
+      <c r="AN17" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AO17" s="44" t="inlineStr"/>
       <c r="AP17" s="44" t="inlineStr"/>
-      <c r="AQ17" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ17" s="44" t="inlineStr"/>
       <c r="AR17" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5359,7 +5480,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU17" s="44" t="inlineStr"/>
+      <c r="AU17" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV17" s="44" t="inlineStr"/>
       <c r="AW17" s="44" t="inlineStr"/>
       <c r="AX17" s="44" t="inlineStr"/>
@@ -5437,19 +5562,15 @@
       <c r="AJ18" s="44" t="inlineStr"/>
       <c r="AK18" s="44" t="inlineStr"/>
       <c r="AL18" s="44" t="inlineStr"/>
-      <c r="AM18" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AN18" s="44" t="inlineStr"/>
+      <c r="AM18" s="44" t="inlineStr"/>
+      <c r="AN18" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AO18" s="44" t="inlineStr"/>
       <c r="AP18" s="44" t="inlineStr"/>
-      <c r="AQ18" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ18" s="44" t="inlineStr"/>
       <c r="AR18" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5465,7 +5586,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU18" s="44" t="inlineStr"/>
+      <c r="AU18" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV18" s="44" t="inlineStr"/>
       <c r="AW18" s="44" t="inlineStr"/>
       <c r="AX18" s="44" t="inlineStr"/>
@@ -5559,11 +5684,7 @@
       <c r="AN19" s="44" t="inlineStr"/>
       <c r="AO19" s="44" t="inlineStr"/>
       <c r="AP19" s="44" t="inlineStr"/>
-      <c r="AQ19" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ19" s="44" t="inlineStr"/>
       <c r="AR19" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5579,7 +5700,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU19" s="44" t="inlineStr"/>
+      <c r="AU19" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV19" s="44" t="inlineStr"/>
       <c r="AW19" s="44" t="inlineStr"/>
       <c r="AX19" s="44" t="inlineStr"/>
@@ -5673,11 +5798,7 @@
       <c r="AN20" s="44" t="inlineStr"/>
       <c r="AO20" s="44" t="inlineStr"/>
       <c r="AP20" s="44" t="inlineStr"/>
-      <c r="AQ20" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ20" s="44" t="inlineStr"/>
       <c r="AR20" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5693,7 +5814,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU20" s="44" t="inlineStr"/>
+      <c r="AU20" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV20" s="44" t="inlineStr"/>
       <c r="AW20" s="44" t="inlineStr"/>
       <c r="AX20" s="44" t="inlineStr"/>
@@ -6584,28 +6709,32 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AD28" s="44" t="inlineStr"/>
+      <c r="AD28" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE28" s="44" t="inlineStr"/>
-      <c r="AF28" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG28" s="44" t="inlineStr"/>
+      <c r="AF28" s="44" t="inlineStr"/>
+      <c r="AG28" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH28" s="44" t="inlineStr"/>
       <c r="AI28" s="44" t="inlineStr"/>
-      <c r="AJ28" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK28" s="44" t="inlineStr"/>
-      <c r="AL28" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AM28" s="44" t="inlineStr"/>
+      <c r="AJ28" s="44" t="inlineStr"/>
+      <c r="AK28" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AL28" s="44" t="inlineStr"/>
+      <c r="AM28" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AN28" s="44" t="inlineStr"/>
       <c r="AO28" s="44" t="inlineStr"/>
       <c r="AP28" s="44" t="inlineStr"/>
@@ -6615,11 +6744,7 @@
       <c r="AT28" s="44" t="inlineStr"/>
       <c r="AU28" s="44" t="inlineStr"/>
       <c r="AV28" s="44" t="inlineStr"/>
-      <c r="AW28" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AW28" s="44" t="inlineStr"/>
       <c r="AX28" s="44" t="inlineStr"/>
       <c r="AY28" s="44" t="inlineStr"/>
       <c r="AZ28" s="44" t="inlineStr"/>
@@ -6730,28 +6855,32 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AD29" s="44" t="inlineStr"/>
+      <c r="AD29" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE29" s="44" t="inlineStr"/>
-      <c r="AF29" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG29" s="44" t="inlineStr"/>
+      <c r="AF29" s="44" t="inlineStr"/>
+      <c r="AG29" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH29" s="44" t="inlineStr"/>
       <c r="AI29" s="44" t="inlineStr"/>
-      <c r="AJ29" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK29" s="44" t="inlineStr"/>
-      <c r="AL29" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AM29" s="44" t="inlineStr"/>
+      <c r="AJ29" s="44" t="inlineStr"/>
+      <c r="AK29" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AL29" s="44" t="inlineStr"/>
+      <c r="AM29" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AN29" s="44" t="inlineStr"/>
       <c r="AO29" s="44" t="inlineStr"/>
       <c r="AP29" s="44" t="inlineStr"/>
@@ -6761,11 +6890,7 @@
       <c r="AT29" s="44" t="inlineStr"/>
       <c r="AU29" s="44" t="inlineStr"/>
       <c r="AV29" s="44" t="inlineStr"/>
-      <c r="AW29" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AW29" s="44" t="inlineStr"/>
       <c r="AX29" s="50" t="inlineStr">
         <is>
           <t>X</t>
@@ -6882,20 +7007,20 @@
       </c>
       <c r="AD30" s="44" t="inlineStr"/>
       <c r="AE30" s="44" t="inlineStr"/>
-      <c r="AF30" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG30" s="44" t="inlineStr"/>
+      <c r="AF30" s="44" t="inlineStr"/>
+      <c r="AG30" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH30" s="44" t="inlineStr"/>
       <c r="AI30" s="44" t="inlineStr"/>
-      <c r="AJ30" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK30" s="44" t="inlineStr"/>
+      <c r="AJ30" s="44" t="inlineStr"/>
+      <c r="AK30" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL30" s="44" t="inlineStr"/>
       <c r="AM30" s="44" t="inlineStr"/>
       <c r="AN30" s="44" t="inlineStr"/>
@@ -7024,20 +7149,20 @@
       </c>
       <c r="AD31" s="44" t="inlineStr"/>
       <c r="AE31" s="44" t="inlineStr"/>
-      <c r="AF31" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG31" s="44" t="inlineStr"/>
+      <c r="AF31" s="44" t="inlineStr"/>
+      <c r="AG31" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH31" s="44" t="inlineStr"/>
       <c r="AI31" s="44" t="inlineStr"/>
-      <c r="AJ31" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK31" s="44" t="inlineStr"/>
+      <c r="AJ31" s="44" t="inlineStr"/>
+      <c r="AK31" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL31" s="44" t="inlineStr"/>
       <c r="AM31" s="44" t="inlineStr"/>
       <c r="AN31" s="44" t="inlineStr"/>
@@ -7169,35 +7294,31 @@
         </is>
       </c>
       <c r="AD32" s="44" t="inlineStr"/>
-      <c r="AE32" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF32" s="44" t="inlineStr"/>
-      <c r="AG32" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH32" s="44" t="inlineStr"/>
-      <c r="AI32" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AJ32" s="44" t="inlineStr"/>
+      <c r="AE32" s="44" t="inlineStr"/>
+      <c r="AF32" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG32" s="44" t="inlineStr"/>
+      <c r="AH32" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AI32" s="44" t="inlineStr"/>
+      <c r="AJ32" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK32" s="44" t="inlineStr"/>
       <c r="AL32" s="44" t="inlineStr"/>
       <c r="AM32" s="44" t="inlineStr"/>
       <c r="AN32" s="44" t="inlineStr"/>
       <c r="AO32" s="44" t="inlineStr"/>
-      <c r="AP32" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AQ32" s="52" t="inlineStr">
+      <c r="AP32" s="44" t="inlineStr"/>
+      <c r="AQ32" s="49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7217,7 +7338,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU32" s="44" t="inlineStr"/>
+      <c r="AU32" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV32" s="44" t="inlineStr"/>
       <c r="AW32" s="44" t="inlineStr"/>
       <c r="AX32" s="44" t="inlineStr"/>
@@ -7301,29 +7426,25 @@
       <c r="AD33" s="44" t="inlineStr"/>
       <c r="AE33" s="44" t="inlineStr"/>
       <c r="AF33" s="44" t="inlineStr"/>
-      <c r="AG33" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH33" s="44" t="inlineStr"/>
-      <c r="AI33" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AJ33" s="44" t="inlineStr"/>
+      <c r="AG33" s="44" t="inlineStr"/>
+      <c r="AH33" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AI33" s="44" t="inlineStr"/>
+      <c r="AJ33" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK33" s="44" t="inlineStr"/>
       <c r="AL33" s="44" t="inlineStr"/>
       <c r="AM33" s="44" t="inlineStr"/>
       <c r="AN33" s="44" t="inlineStr"/>
       <c r="AO33" s="44" t="inlineStr"/>
       <c r="AP33" s="44" t="inlineStr"/>
-      <c r="AQ33" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ33" s="44" t="inlineStr"/>
       <c r="AR33" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7339,7 +7460,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU33" s="44" t="inlineStr"/>
+      <c r="AU33" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV33" s="44" t="inlineStr"/>
       <c r="AW33" s="44" t="inlineStr"/>
       <c r="AX33" s="44" t="inlineStr"/>
@@ -7423,29 +7548,25 @@
       <c r="AD34" s="44" t="inlineStr"/>
       <c r="AE34" s="44" t="inlineStr"/>
       <c r="AF34" s="44" t="inlineStr"/>
-      <c r="AG34" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH34" s="44" t="inlineStr"/>
-      <c r="AI34" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AJ34" s="44" t="inlineStr"/>
+      <c r="AG34" s="44" t="inlineStr"/>
+      <c r="AH34" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AI34" s="44" t="inlineStr"/>
+      <c r="AJ34" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK34" s="44" t="inlineStr"/>
       <c r="AL34" s="44" t="inlineStr"/>
       <c r="AM34" s="44" t="inlineStr"/>
       <c r="AN34" s="44" t="inlineStr"/>
       <c r="AO34" s="44" t="inlineStr"/>
       <c r="AP34" s="44" t="inlineStr"/>
-      <c r="AQ34" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ34" s="44" t="inlineStr"/>
       <c r="AR34" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7461,7 +7582,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU34" s="44" t="inlineStr"/>
+      <c r="AU34" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV34" s="44" t="inlineStr"/>
       <c r="AW34" s="44" t="inlineStr"/>
       <c r="AX34" s="44" t="inlineStr"/>
@@ -7556,18 +7681,14 @@
       <c r="AK35" s="44" t="inlineStr"/>
       <c r="AL35" s="44" t="inlineStr"/>
       <c r="AM35" s="44" t="inlineStr"/>
-      <c r="AN35" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO35" s="44" t="inlineStr"/>
+      <c r="AN35" s="44" t="inlineStr"/>
+      <c r="AO35" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP35" s="44" t="inlineStr"/>
-      <c r="AQ35" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ35" s="44" t="inlineStr"/>
       <c r="AR35" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7583,7 +7704,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU35" s="44" t="inlineStr"/>
+      <c r="AU35" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV35" s="44" t="inlineStr"/>
       <c r="AW35" s="44" t="inlineStr"/>
       <c r="AX35" s="44" t="inlineStr"/>
@@ -7678,18 +7803,14 @@
       <c r="AK36" s="44" t="inlineStr"/>
       <c r="AL36" s="44" t="inlineStr"/>
       <c r="AM36" s="44" t="inlineStr"/>
-      <c r="AN36" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO36" s="44" t="inlineStr"/>
+      <c r="AN36" s="44" t="inlineStr"/>
+      <c r="AO36" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP36" s="44" t="inlineStr"/>
-      <c r="AQ36" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ36" s="44" t="inlineStr"/>
       <c r="AR36" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7705,7 +7826,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU36" s="44" t="inlineStr"/>
+      <c r="AU36" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV36" s="44" t="inlineStr"/>
       <c r="AW36" s="44" t="inlineStr"/>
       <c r="AX36" s="44" t="inlineStr"/>
@@ -7800,18 +7925,14 @@
       <c r="AK37" s="44" t="inlineStr"/>
       <c r="AL37" s="44" t="inlineStr"/>
       <c r="AM37" s="44" t="inlineStr"/>
-      <c r="AN37" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO37" s="44" t="inlineStr"/>
+      <c r="AN37" s="44" t="inlineStr"/>
+      <c r="AO37" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP37" s="44" t="inlineStr"/>
-      <c r="AQ37" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ37" s="44" t="inlineStr"/>
       <c r="AR37" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7827,7 +7948,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU37" s="44" t="inlineStr"/>
+      <c r="AU37" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV37" s="44" t="inlineStr"/>
       <c r="AW37" s="44" t="inlineStr"/>
       <c r="AX37" s="44" t="inlineStr"/>
@@ -7922,18 +8047,14 @@
       <c r="AK38" s="44" t="inlineStr"/>
       <c r="AL38" s="44" t="inlineStr"/>
       <c r="AM38" s="44" t="inlineStr"/>
-      <c r="AN38" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO38" s="44" t="inlineStr"/>
+      <c r="AN38" s="44" t="inlineStr"/>
+      <c r="AO38" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP38" s="44" t="inlineStr"/>
-      <c r="AQ38" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ38" s="44" t="inlineStr"/>
       <c r="AR38" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7949,7 +8070,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU38" s="44" t="inlineStr"/>
+      <c r="AU38" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV38" s="44" t="inlineStr"/>
       <c r="AW38" s="44" t="inlineStr"/>
       <c r="AX38" s="44" t="inlineStr"/>
@@ -8388,36 +8513,32 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AD42" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AE42" s="44" t="inlineStr"/>
+      <c r="AD42" s="44" t="inlineStr"/>
+      <c r="AE42" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AF42" s="44" t="inlineStr"/>
       <c r="AG42" s="44" t="inlineStr"/>
-      <c r="AH42" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AH42" s="44" t="inlineStr"/>
       <c r="AI42" s="48" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="AJ42" s="44" t="inlineStr"/>
+      <c r="AJ42" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK42" s="44" t="inlineStr"/>
       <c r="AL42" s="44" t="inlineStr"/>
       <c r="AM42" s="44" t="inlineStr"/>
       <c r="AN42" s="44" t="inlineStr"/>
       <c r="AO42" s="44" t="inlineStr"/>
       <c r="AP42" s="44" t="inlineStr"/>
-      <c r="AQ42" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ42" s="44" t="inlineStr"/>
       <c r="AR42" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -8433,7 +8554,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU42" s="44" t="inlineStr"/>
+      <c r="AU42" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV42" s="44" t="inlineStr"/>
       <c r="AW42" s="44" t="inlineStr"/>
       <c r="AX42" s="44" t="inlineStr"/>
@@ -8509,17 +8634,13 @@
       <c r="AL43" s="44" t="inlineStr"/>
       <c r="AM43" s="44" t="inlineStr"/>
       <c r="AN43" s="44" t="inlineStr"/>
-      <c r="AO43" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AO43" s="44" t="inlineStr"/>
       <c r="AP43" s="49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="AQ43" s="52" t="inlineStr">
+      <c r="AQ43" s="49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8539,7 +8660,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU43" s="44" t="inlineStr"/>
+      <c r="AU43" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AV43" s="44" t="inlineStr"/>
       <c r="AW43" s="44" t="inlineStr"/>
       <c r="AX43" s="44" t="inlineStr"/>
@@ -8626,26 +8751,22 @@
       <c r="AG44" s="44" t="inlineStr"/>
       <c r="AH44" s="44" t="inlineStr"/>
       <c r="AI44" s="44" t="inlineStr"/>
-      <c r="AJ44" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK44" s="44" t="inlineStr"/>
+      <c r="AJ44" s="44" t="inlineStr"/>
+      <c r="AK44" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL44" s="44" t="inlineStr"/>
       <c r="AM44" s="44" t="inlineStr"/>
-      <c r="AN44" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO44" s="44" t="inlineStr"/>
+      <c r="AN44" s="44" t="inlineStr"/>
+      <c r="AO44" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP44" s="44" t="inlineStr"/>
-      <c r="AQ44" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ44" s="44" t="inlineStr"/>
       <c r="AR44" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -8661,12 +8782,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU44" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV44" s="44" t="inlineStr"/>
+      <c r="AU44" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AV44" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW44" s="44" t="inlineStr"/>
       <c r="AX44" s="44" t="inlineStr"/>
       <c r="AY44" s="44" t="inlineStr"/>
@@ -8780,34 +8905,30 @@
       </c>
       <c r="AD45" s="44" t="inlineStr"/>
       <c r="AE45" s="44" t="inlineStr"/>
-      <c r="AF45" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG45" s="44" t="inlineStr"/>
+      <c r="AF45" s="44" t="inlineStr"/>
+      <c r="AG45" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH45" s="44" t="inlineStr"/>
       <c r="AI45" s="44" t="inlineStr"/>
-      <c r="AJ45" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK45" s="44" t="inlineStr"/>
+      <c r="AJ45" s="44" t="inlineStr"/>
+      <c r="AK45" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL45" s="44" t="inlineStr"/>
       <c r="AM45" s="44" t="inlineStr"/>
-      <c r="AN45" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO45" s="44" t="inlineStr"/>
+      <c r="AN45" s="44" t="inlineStr"/>
+      <c r="AO45" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP45" s="44" t="inlineStr"/>
-      <c r="AQ45" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ45" s="44" t="inlineStr"/>
       <c r="AR45" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -8823,12 +8944,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU45" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV45" s="44" t="inlineStr"/>
+      <c r="AU45" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AV45" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW45" s="44" t="inlineStr"/>
       <c r="AX45" s="44" t="inlineStr"/>
       <c r="AY45" s="44" t="inlineStr"/>
@@ -8942,39 +9067,39 @@
       </c>
       <c r="AD46" s="44" t="inlineStr"/>
       <c r="AE46" s="44" t="inlineStr"/>
-      <c r="AF46" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG46" s="44" t="inlineStr"/>
+      <c r="AF46" s="44" t="inlineStr"/>
+      <c r="AG46" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH46" s="44" t="inlineStr"/>
       <c r="AI46" s="44" t="inlineStr"/>
-      <c r="AJ46" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK46" s="44" t="inlineStr"/>
+      <c r="AJ46" s="44" t="inlineStr"/>
+      <c r="AK46" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL46" s="44" t="inlineStr"/>
       <c r="AM46" s="44" t="inlineStr"/>
-      <c r="AN46" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO46" s="44" t="inlineStr"/>
+      <c r="AN46" s="44" t="inlineStr"/>
+      <c r="AO46" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP46" s="44" t="inlineStr"/>
       <c r="AQ46" s="44" t="inlineStr"/>
       <c r="AR46" s="44" t="inlineStr"/>
       <c r="AS46" s="44" t="inlineStr"/>
       <c r="AT46" s="44" t="inlineStr"/>
-      <c r="AU46" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV46" s="44" t="inlineStr"/>
+      <c r="AU46" s="44" t="inlineStr"/>
+      <c r="AV46" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW46" s="44" t="inlineStr"/>
       <c r="AX46" s="44" t="inlineStr"/>
       <c r="AY46" s="44" t="inlineStr"/>
@@ -9060,26 +9185,22 @@
       <c r="AG47" s="44" t="inlineStr"/>
       <c r="AH47" s="44" t="inlineStr"/>
       <c r="AI47" s="44" t="inlineStr"/>
-      <c r="AJ47" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK47" s="44" t="inlineStr"/>
+      <c r="AJ47" s="44" t="inlineStr"/>
+      <c r="AK47" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL47" s="44" t="inlineStr"/>
       <c r="AM47" s="44" t="inlineStr"/>
-      <c r="AN47" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO47" s="44" t="inlineStr"/>
+      <c r="AN47" s="44" t="inlineStr"/>
+      <c r="AO47" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP47" s="44" t="inlineStr"/>
-      <c r="AQ47" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ47" s="44" t="inlineStr"/>
       <c r="AR47" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -9095,12 +9216,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU47" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV47" s="44" t="inlineStr"/>
+      <c r="AU47" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AV47" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW47" s="44" t="inlineStr"/>
       <c r="AX47" s="44" t="inlineStr"/>
       <c r="AY47" s="44" t="inlineStr"/>
@@ -9214,34 +9339,30 @@
       </c>
       <c r="AD48" s="44" t="inlineStr"/>
       <c r="AE48" s="44" t="inlineStr"/>
-      <c r="AF48" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG48" s="44" t="inlineStr"/>
+      <c r="AF48" s="44" t="inlineStr"/>
+      <c r="AG48" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH48" s="44" t="inlineStr"/>
       <c r="AI48" s="44" t="inlineStr"/>
-      <c r="AJ48" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK48" s="44" t="inlineStr"/>
+      <c r="AJ48" s="44" t="inlineStr"/>
+      <c r="AK48" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL48" s="44" t="inlineStr"/>
       <c r="AM48" s="44" t="inlineStr"/>
-      <c r="AN48" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO48" s="44" t="inlineStr"/>
+      <c r="AN48" s="44" t="inlineStr"/>
+      <c r="AO48" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP48" s="44" t="inlineStr"/>
-      <c r="AQ48" s="52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AQ48" s="44" t="inlineStr"/>
       <c r="AR48" s="52" t="inlineStr">
         <is>
           <t>X</t>
@@ -9257,12 +9378,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AU48" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV48" s="44" t="inlineStr"/>
+      <c r="AU48" s="52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AV48" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW48" s="44" t="inlineStr"/>
       <c r="AX48" s="44" t="inlineStr"/>
       <c r="AY48" s="44" t="inlineStr"/>
@@ -9376,39 +9501,39 @@
       </c>
       <c r="AD49" s="44" t="inlineStr"/>
       <c r="AE49" s="44" t="inlineStr"/>
-      <c r="AF49" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG49" s="44" t="inlineStr"/>
+      <c r="AF49" s="44" t="inlineStr"/>
+      <c r="AG49" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AH49" s="44" t="inlineStr"/>
       <c r="AI49" s="44" t="inlineStr"/>
-      <c r="AJ49" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK49" s="44" t="inlineStr"/>
+      <c r="AJ49" s="44" t="inlineStr"/>
+      <c r="AK49" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL49" s="44" t="inlineStr"/>
       <c r="AM49" s="44" t="inlineStr"/>
-      <c r="AN49" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AO49" s="44" t="inlineStr"/>
+      <c r="AN49" s="44" t="inlineStr"/>
+      <c r="AO49" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AP49" s="44" t="inlineStr"/>
       <c r="AQ49" s="44" t="inlineStr"/>
       <c r="AR49" s="44" t="inlineStr"/>
       <c r="AS49" s="44" t="inlineStr"/>
       <c r="AT49" s="44" t="inlineStr"/>
-      <c r="AU49" s="50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AV49" s="44" t="inlineStr"/>
+      <c r="AU49" s="44" t="inlineStr"/>
+      <c r="AV49" s="50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AW49" s="44" t="inlineStr"/>
       <c r="AX49" s="44" t="inlineStr"/>
       <c r="AY49" s="44" t="inlineStr"/>
@@ -9534,12 +9659,12 @@
       <c r="AG50" s="44" t="inlineStr"/>
       <c r="AH50" s="44" t="inlineStr"/>
       <c r="AI50" s="44" t="inlineStr"/>
-      <c r="AJ50" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK50" s="44" t="inlineStr"/>
+      <c r="AJ50" s="44" t="inlineStr"/>
+      <c r="AK50" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL50" s="44" t="inlineStr"/>
       <c r="AM50" s="44" t="inlineStr"/>
       <c r="AN50" s="44" t="inlineStr"/>
@@ -9680,12 +9805,12 @@
       <c r="AG51" s="44" t="inlineStr"/>
       <c r="AH51" s="44" t="inlineStr"/>
       <c r="AI51" s="44" t="inlineStr"/>
-      <c r="AJ51" s="48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AK51" s="44" t="inlineStr"/>
+      <c r="AJ51" s="44" t="inlineStr"/>
+      <c r="AK51" s="48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AL51" s="44" t="inlineStr"/>
       <c r="AM51" s="44" t="inlineStr"/>
       <c r="AN51" s="44" t="inlineStr"/>
@@ -10105,14 +10230,14 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="AQ1:AT1"/>
+    <mergeCell ref="AR1:AU1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AU1:BA1"/>
+    <mergeCell ref="AV1:BA1"/>
     <mergeCell ref="U1:AC1"/>
-    <mergeCell ref="AD1:AL1"/>
-    <mergeCell ref="AM1:AP1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="AN1:AQ1"/>
+    <mergeCell ref="AD1:AM1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10345,7 +10470,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Immer dabei</t>
+          <t>Montagematerial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10373,7 +10498,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Immer dabei</t>
+          <t>Montagematerial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10401,7 +10526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Immer dabei</t>
+          <t>Montagematerial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10744,7 +10869,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3431 102</t>
+          <t>2141 298</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10754,25 +10879,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Einlaufgarnitur Laufen, Einlaufmanschette ½", zu Urinoir 3421</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Einlaufgarnitur Laufen, Einlaufmanschette ½", zu Urinoir 3421 103 / 120</t>
-        </is>
-      </c>
+          <t>Einlaufmanschette, zu Urinoir Duravit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3431 110</t>
+          <t>3431 102</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10782,16 +10903,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Einlaufgarnitur Geberit, 1" x 35 mm, Messing, Deckkappe, zu Urinoir</t>
+          <t>Einlaufgarnitur Laufen, Einlaufmanschette ½", zu Urinoir 3421</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Einlaufgarnitur Geberit, 1" x 35 mm, Messing, Deckkappe, zu Urinoir Tamaro/Taro</t>
+          <t>Einlaufgarnitur Laufen, Einlaufmanschette ½", zu Urinoir 3421 103 / 120</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -10800,7 +10921,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3431 250</t>
+          <t>3431 110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10810,25 +10931,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Einlaufmanschette Geberit, Ø 32-35 mm, zu Urinoirs Casa / Fizz / Lema /</t>
+          <t>Einlaufgarnitur Geberit, 1" x 35 mm, Messing, Deckkappe, zu Urinoir</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Einlaufmanschette Geberit, Ø 32- 35 mm, zu Urinoirs Casa / Fizz / Lema / Caprino Plus</t>
+          <t>Einlaufgarnitur Geberit, 1" x 35 mm, Messing, Deckkappe, zu Urinoir Tamaro/Taro</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3441 111</t>
+          <t>3431 250</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10838,21 +10959,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Absaugesiphon Geberit, AP, Abgang waagrecht Ø 40 mm</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Einlaufmanschette Geberit, Ø 32-35 mm, zu Urinoirs Casa / Fizz / Lema /</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Einlaufmanschette Geberit, Ø 32- 35 mm, zu Urinoirs Casa / Fizz / Lema / Caprino Plus</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>81.5</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3441 112</t>
+          <t>3441 111</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10862,25 +10987,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Absaugesiphon Geberit, AP, Konduktivsonden, Abgang waagrecht Ø 40</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Absaugesiphon Geberit, AP, Konduktivsonden, Abgang waagrecht Ø 40 mm</t>
-        </is>
-      </c>
+          <t>Absaugesiphon Geberit, AP, Abgang waagrecht Ø 40 mm</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>90.5</v>
+        <v>81.5</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3441 120</t>
+          <t>3441 112</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10888,16 +11009,27 @@
           <t>Ablauf &amp; Einlauf</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Absaugesiphon Geberit, AP, Konduktivsonden, Abgang waagrecht Ø 40</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Absaugesiphon Geberit, AP, Konduktivsonden, Abgang waagrecht Ø 40 mm</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>90.5</v>
+      </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3441 150</t>
+          <t>3441 120</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10905,23 +11037,16 @@
           <t>Ablauf &amp; Einlauf</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Absaugesiphon Geberit AP, waagrecht Ø 40 mm, zu Urinoir</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="n">
-        <v>76.5</v>
-      </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8111 412</t>
+          <t>3441 150</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10929,16 +11054,23 @@
           <t>Ablauf &amp; Einlauf</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Absaugesiphon Geberit AP, waagrecht Ø 40 mm, zu Urinoir</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>76.5</v>
+      </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8111 428</t>
+          <t>8111 412</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10946,42 +11078,31 @@
           <t>Ablauf &amp; Einlauf</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Steckdichtung, Ø 51 / 40 mm</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
-        <v>4.8</v>
-      </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3962 155</t>
+          <t>8111 428</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Befestigung</t>
+          <t>Ablauf &amp; Einlauf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gewindebolzen-Set M8 / M12 zu Duofix Lema (H8940620000001)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Gewindebolzen Laufen M8 / M12 zu Duofix Lema Ausführung bis 2010 (H8940620000001)</t>
-        </is>
-      </c>
+          <t>Steckdichtung, Ø 51 / 40 mm</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>41.5</v>
+        <v>4.8</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -10990,7 +11111,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3962 156</t>
+          <t>3962 155</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11000,25 +11121,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gewindebolzen Umbauset M12 (H8928140000001)</t>
+          <t>Gewindebolzen-Set M8 / M12 zu Duofix Lema (H8940620000001)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gewindebolzen Umbauset M12 Laufen zu Urinoir Lema, Alessi Caprino (H8928140000001)</t>
+          <t>Gewindebolzen Laufen M8 / M12 zu Duofix Lema Ausführung bis 2010 (H8940620000001)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>41.5</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8211 112</t>
+          <t>3962 156</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11026,16 +11147,27 @@
           <t>Befestigung</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gewindebolzen Umbauset M12 (H8928140000001)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Gewindebolzen Umbauset M12 Laufen zu Urinoir Lema, Alessi Caprino (H8928140000001)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>27</v>
+      </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8211 210</t>
+          <t>8211 112</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11043,44 +11175,44 @@
           <t>Befestigung</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Abdeckkappe, Klemmscheiben, Set à 2 Stück, Weiss</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Abdeckkappen-Set Geberit Klemmscheiben, Set à 2 Stück</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2112 890</t>
+          <t>8211 210</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trennwand</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>Befestigung</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Abdeckkappe, Klemmscheiben, Set à 2 Stück, Weiss</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Abdeckkappen-Set Geberit Klemmscheiben, Set à 2 Stück</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>14.5</v>
+      </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3482 117</t>
+          <t>2112 890</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11088,19 +11220,8 @@
           <t>Trennwand</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Trennwand Geberit, Glas weiss, 75 x 43 cm, Befestigungsmaterial</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Trennwand Geberit 75 x 43 cm Glas weiss Befestigungsmaterial</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>976</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>27</v>
       </c>
@@ -11108,7 +11229,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3482 118</t>
+          <t>3482 117</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11118,12 +11239,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trennwand Geberit, Glas anthrazit, 75 x 43 cm, Befestigungsmaterial</t>
+          <t>Trennwand Geberit, Glas weiss, 75 x 43 cm, Befestigungsmaterial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Trennwand Geberit 75 x 43 cm Glas anthrazit Befestigungsmaterial</t>
+          <t>Trennwand Geberit 75 x 43 cm Glas weiss Befestigungsmaterial</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -11136,7 +11257,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3482 119</t>
+          <t>3482 118</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11146,12 +11267,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Trennwand Geberit, Glas umbra, 75 x 43 cm, Befestigungsmaterial</t>
+          <t>Trennwand Geberit, Glas anthrazit, 75 x 43 cm, Befestigungsmaterial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Trennwand Geberit 75 x 43 cm Glas umbra Befestigungsmaterial</t>
+          <t>Trennwand Geberit 75 x 43 cm Glas anthrazit Befestigungsmaterial</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -11164,24 +11285,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2112 889</t>
+          <t>3482 119</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Weiteres</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>Trennwand</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Trennwand Geberit, Glas umbra, 75 x 43 cm, Befestigungsmaterial</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Trennwand Geberit 75 x 43 cm Glas umbra Befestigungsmaterial</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>976</v>
+      </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2121 198</t>
+          <t>2112 889</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11192,13 +11324,13 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2141 298</t>
+          <t>2121 198</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11206,17 +11338,10 @@
           <t>Weiteres</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Einlaufmanschette, zu Urinoir Duravit</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>33</v>
-      </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
